--- a/tests/fixtures/vested-sample.xlsx
+++ b/tests/fixtures/vested-sample.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Trades" sheetId="1" r:id="rId1"/>
+    <sheet name="User Details" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Holdings" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,9 +399,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:E2"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="31"/>
+    <col min="1" max="1" customWidth="1" width="18"/>
+    <col min="2" max="2" customWidth="1" width="34"/>
+    <col min="3" max="3" customWidth="1" width="11"/>
+    <col min="4" max="4" customWidth="1" width="27"/>
+    <col min="5" max="5" customWidth="1" width="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Period</v>
+      </c>
+      <c r="B1" t="str">
+        <v>User</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Govt Id</v>
+      </c>
+      <c r="D1" t="str">
+        <v>DriveWealth Account Number</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>As of 14 May 2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ujjwal Gupta (Uttar Pradesh, IND)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CHKPG6915R</v>
+      </c>
+      <c r="D2" t="str">
+        <v>VSTJ000519</v>
+      </c>
+      <c r="E2" t="str">
+        <v>gupta.ujjwal14@gmail.com</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="27"/>
+    <col min="2" max="2" customWidth="1" width="28"/>
+    <col min="3" max="3" customWidth="1" width="25"/>
+    <col min="4" max="4" customWidth="1" width="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Current Equity Value (USD)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Total Amount Invested (USD)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Investment Returns (USD)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Investment Returns (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>19,241.95</v>
+      </c>
+      <c r="B2" t="str">
+        <v>13,386.41</v>
+      </c>
+      <c r="C2" t="str">
+        <v>5,855.54</v>
+      </c>
+      <c r="D2" t="str">
+        <v>43.74%</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K21"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="48"/>
     <col min="2" max="2" customWidth="1" width="7"/>
     <col min="3" max="3" customWidth="1" width="18"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -449,7 +548,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Apple Inc</v>
+        <v>Apple, Inc.</v>
       </c>
       <c r="B2" t="str">
         <v>AAPL</v>
@@ -458,28 +557,28 @@
         <v>2.7</v>
       </c>
       <c r="D2">
-        <v>195.27</v>
+        <v>298.87</v>
       </c>
       <c r="E2">
-        <v>527.23</v>
+        <v>806.95</v>
       </c>
       <c r="F2">
-        <v>215.19</v>
+        <v>215.72</v>
       </c>
       <c r="G2">
-        <v>581.02</v>
+        <v>582.45</v>
       </c>
       <c r="H2">
-        <v>-53.79</v>
+        <v>224.5</v>
       </c>
       <c r="I2">
-        <v>-9.26</v>
+        <v>38.54</v>
       </c>
       <c r="J2">
-        <v>-16.44</v>
+        <v>10.99</v>
       </c>
       <c r="K2">
-        <v>-3.02</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="3">
@@ -490,66 +589,66 @@
         <v>AMD</v>
       </c>
       <c r="C3">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="D3">
-        <v>110.31</v>
+        <v>445.5</v>
       </c>
       <c r="E3">
-        <v>375.05</v>
+        <v>1960.2</v>
       </c>
       <c r="F3">
-        <v>106.66</v>
+        <v>132.37</v>
       </c>
       <c r="G3">
-        <v>362.66</v>
+        <v>582.41</v>
       </c>
       <c r="H3">
-        <v>12.39</v>
+        <v>1377.79</v>
       </c>
       <c r="I3">
-        <v>3.42</v>
+        <v>236.57</v>
       </c>
       <c r="J3">
-        <v>-1.36</v>
+        <v>-12.28</v>
       </c>
       <c r="K3">
-        <v>-0.36</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Amazon.com Inc</v>
+        <v>Amazon.com Inc.</v>
       </c>
       <c r="B4" t="str">
         <v>AMZN</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>6.05</v>
       </c>
       <c r="D4">
-        <v>200.99</v>
+        <v>270.13</v>
       </c>
       <c r="E4">
-        <v>854.21</v>
+        <v>1634.29</v>
       </c>
       <c r="F4">
-        <v>197.46</v>
+        <v>207.4</v>
       </c>
       <c r="G4">
-        <v>839.19</v>
+        <v>1254.74</v>
       </c>
       <c r="H4">
-        <v>15.02</v>
+        <v>379.55</v>
       </c>
       <c r="I4">
-        <v>1.79</v>
+        <v>30.25</v>
       </c>
       <c r="J4">
-        <v>-8.97</v>
+        <v>26.08</v>
       </c>
       <c r="K4">
-        <v>-1.04</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="5">
@@ -560,31 +659,31 @@
         <v>ASML</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="D5">
-        <v>732.48</v>
+        <v>1581.58</v>
       </c>
       <c r="E5">
-        <v>439.49</v>
+        <v>1739.74</v>
       </c>
       <c r="F5">
-        <v>735.1</v>
+        <v>732.13</v>
       </c>
       <c r="G5">
-        <v>441.06</v>
+        <v>805.34</v>
       </c>
       <c r="H5">
-        <v>-1.57</v>
+        <v>934.4</v>
       </c>
       <c r="I5">
-        <v>-0.36</v>
+        <v>116.03</v>
       </c>
       <c r="J5">
-        <v>-4.93</v>
+        <v>66.7</v>
       </c>
       <c r="K5">
-        <v>-1.11</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="6">
@@ -598,28 +697,28 @@
         <v>0.5</v>
       </c>
       <c r="D6">
-        <v>285.22</v>
+        <v>309.62</v>
       </c>
       <c r="E6">
-        <v>142.61</v>
+        <v>154.81</v>
       </c>
       <c r="F6">
-        <v>277.45</v>
+        <v>278.12</v>
       </c>
       <c r="G6">
-        <v>138.72</v>
+        <v>139.06</v>
       </c>
       <c r="H6">
-        <v>3.89</v>
+        <v>15.75</v>
       </c>
       <c r="I6">
-        <v>2.8</v>
+        <v>11.33</v>
       </c>
       <c r="J6">
-        <v>-0.98</v>
+        <v>-2.35</v>
       </c>
       <c r="K6">
-        <v>-0.68</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="7">
@@ -633,28 +732,28 @@
         <v>70</v>
       </c>
       <c r="D7">
-        <v>5.99</v>
+        <v>9.39</v>
       </c>
       <c r="E7">
-        <v>419.3</v>
+        <v>657.3</v>
       </c>
       <c r="F7">
-        <v>6.34</v>
+        <v>6.36</v>
       </c>
       <c r="G7">
-        <v>444.01</v>
+        <v>445.11</v>
       </c>
       <c r="H7">
-        <v>-24.71</v>
+        <v>212.19</v>
       </c>
       <c r="I7">
-        <v>-5.57</v>
+        <v>47.67</v>
       </c>
       <c r="J7">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>-1.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -665,31 +764,31 @@
         <v>GOOGL</v>
       </c>
       <c r="C8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>168.47</v>
+        <v>402.62</v>
       </c>
       <c r="E8">
-        <v>741.27</v>
+        <v>1811.79</v>
       </c>
       <c r="F8">
-        <v>168.14</v>
+        <v>162.46</v>
       </c>
       <c r="G8">
-        <v>739.82</v>
+        <v>731.07</v>
       </c>
       <c r="H8">
-        <v>1.45</v>
+        <v>1080.72</v>
       </c>
       <c r="I8">
-        <v>0.2</v>
+        <v>147.83</v>
       </c>
       <c r="J8">
-        <v>-10.56</v>
+        <v>68.72</v>
       </c>
       <c r="K8">
-        <v>-1.4</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="9">
@@ -700,36 +799,36 @@
         <v>KTEC</v>
       </c>
       <c r="C9">
-        <v>59.32</v>
+        <v>63.32</v>
       </c>
       <c r="D9">
-        <v>15.78</v>
+        <v>14.87</v>
       </c>
       <c r="E9">
-        <v>936.07</v>
+        <v>941.57</v>
       </c>
       <c r="F9">
-        <v>16.25</v>
+        <v>15.93</v>
       </c>
       <c r="G9">
-        <v>964.11</v>
+        <v>1008.59</v>
       </c>
       <c r="H9">
-        <v>-28.04</v>
+        <v>-67.02</v>
       </c>
       <c r="I9">
-        <v>-2.91</v>
+        <v>-6.64</v>
       </c>
       <c r="J9">
-        <v>-2.37</v>
+        <v>42.42</v>
       </c>
       <c r="K9">
-        <v>-0.25</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mastercard Inc</v>
+        <v>MasterCard Inc.</v>
       </c>
       <c r="B10" t="str">
         <v>MA</v>
@@ -738,28 +837,28 @@
         <v>0.2</v>
       </c>
       <c r="D10">
-        <v>563.6</v>
+        <v>490.65</v>
       </c>
       <c r="E10">
-        <v>112.72</v>
+        <v>98.13</v>
       </c>
       <c r="F10">
-        <v>560.3</v>
+        <v>561.65</v>
       </c>
       <c r="G10">
-        <v>112.06</v>
+        <v>112.33</v>
       </c>
       <c r="H10">
-        <v>0.66</v>
+        <v>-14.2</v>
       </c>
       <c r="I10">
-        <v>0.59</v>
+        <v>-12.64</v>
       </c>
       <c r="J10">
-        <v>-1.31</v>
+        <v>-1.83</v>
       </c>
       <c r="K10">
-        <v>-1.15</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="11">
@@ -773,208 +872,383 @@
         <v>15</v>
       </c>
       <c r="D11">
-        <v>13.46</v>
+        <v>18.84</v>
       </c>
       <c r="E11">
-        <v>201.9</v>
+        <v>282.6</v>
       </c>
       <c r="F11">
-        <v>16.56</v>
+        <v>16.6</v>
       </c>
       <c r="G11">
-        <v>248.34</v>
+        <v>248.94</v>
       </c>
       <c r="H11">
-        <v>-46.44</v>
+        <v>33.66</v>
       </c>
       <c r="I11">
-        <v>-18.7</v>
+        <v>13.52</v>
       </c>
       <c r="J11">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="K11">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Microsoft Corporation</v>
+        <v>Mercadolibre, Inc.</v>
       </c>
       <c r="B12" t="str">
-        <v>MSFT</v>
+        <v>MELI</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.427</v>
       </c>
       <c r="D12">
-        <v>450.18</v>
+        <v>1561.99</v>
       </c>
       <c r="E12">
-        <v>450.18</v>
+        <v>666.97</v>
       </c>
       <c r="F12">
-        <v>436.02</v>
+        <v>1652.72</v>
       </c>
       <c r="G12">
-        <v>436.02</v>
+        <v>705.71</v>
       </c>
       <c r="H12">
-        <v>14.16</v>
+        <v>-38.74</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>-5.49</v>
       </c>
       <c r="J12">
-        <v>-4.68</v>
+        <v>-7.17</v>
       </c>
       <c r="K12">
-        <v>-1.03</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>NVIDIA Corporation</v>
+        <v>Meta Platforms Inc</v>
       </c>
       <c r="B13" t="str">
-        <v>NVDA</v>
+        <v>META</v>
       </c>
       <c r="C13">
-        <v>2.725</v>
+        <v>1.97</v>
       </c>
       <c r="D13">
-        <v>131.29</v>
+        <v>616.63</v>
       </c>
       <c r="E13">
-        <v>357.77</v>
+        <v>1214.76</v>
       </c>
       <c r="F13">
-        <v>120.45</v>
+        <v>595.21</v>
       </c>
       <c r="G13">
-        <v>328.23</v>
+        <v>1172.56</v>
       </c>
       <c r="H13">
-        <v>29.54</v>
+        <v>42.2</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="J13">
-        <v>-4.2</v>
+        <v>26.85</v>
       </c>
       <c r="K13">
-        <v>-1.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FIRST TRUST NASDAQ ARTIFICIA</v>
+        <v>Microsoft Corporation</v>
       </c>
       <c r="B14" t="str">
-        <v>ROBT</v>
+        <v>MSFT</v>
       </c>
       <c r="C14">
-        <v>12.5</v>
+        <v>3.39</v>
       </c>
       <c r="D14">
-        <v>44.21</v>
+        <v>405.21</v>
       </c>
       <c r="E14">
-        <v>552.63</v>
+        <v>1373.66</v>
       </c>
       <c r="F14">
-        <v>42.42</v>
+        <v>409.86</v>
       </c>
       <c r="G14">
-        <v>530.24</v>
+        <v>1389.41</v>
       </c>
       <c r="H14">
-        <v>22.39</v>
+        <v>-15.75</v>
       </c>
       <c r="I14">
-        <v>4.22</v>
+        <v>-1.13</v>
       </c>
       <c r="J14">
-        <v>-4.5</v>
+        <v>-8.68</v>
       </c>
       <c r="K14">
-        <v>-0.81</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>iShares Semiconductor ETF</v>
+        <v>NVIDIA Corporation</v>
       </c>
       <c r="B15" t="str">
-        <v>SOXX</v>
+        <v>NVDA</v>
       </c>
       <c r="C15">
-        <v>2.8</v>
+        <v>4.225</v>
       </c>
       <c r="D15">
-        <v>202.56</v>
+        <v>225.83</v>
       </c>
       <c r="E15">
-        <v>567.17</v>
+        <v>954.13</v>
       </c>
       <c r="F15">
-        <v>198.25</v>
+        <v>139.21</v>
       </c>
       <c r="G15">
-        <v>555.1</v>
+        <v>588.15</v>
       </c>
       <c r="H15">
-        <v>12.07</v>
+        <v>365.98</v>
       </c>
       <c r="I15">
-        <v>2.17</v>
+        <v>62.23</v>
       </c>
       <c r="J15">
-        <v>-8.93</v>
+        <v>21.34</v>
       </c>
       <c r="K15">
-        <v>-1.55</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+        <v>Novo Nordisk A/S</v>
       </c>
       <c r="B16" t="str">
+        <v>NVO</v>
+      </c>
+      <c r="C16">
+        <v>17.24</v>
+      </c>
+      <c r="D16">
+        <v>47.08</v>
+      </c>
+      <c r="E16">
+        <v>811.66</v>
+      </c>
+      <c r="F16">
+        <v>47.15</v>
+      </c>
+      <c r="G16">
+        <v>812.79</v>
+      </c>
+      <c r="H16">
+        <v>-1.13</v>
+      </c>
+      <c r="I16">
+        <v>-0.14</v>
+      </c>
+      <c r="J16">
+        <v>1.38</v>
+      </c>
+      <c r="K16">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>FIRST TRUST NASDAQ ARTIFICIA</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ROBT</v>
+      </c>
+      <c r="C17">
+        <v>12.5</v>
+      </c>
+      <c r="D17">
+        <v>53.98</v>
+      </c>
+      <c r="E17">
+        <v>674.75</v>
+      </c>
+      <c r="F17">
+        <v>42.52</v>
+      </c>
+      <c r="G17">
+        <v>531.55</v>
+      </c>
+      <c r="H17">
+        <v>143.2</v>
+      </c>
+      <c r="I17">
+        <v>26.94</v>
+      </c>
+      <c r="J17">
+        <v>3.88</v>
+      </c>
+      <c r="K17">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>iShares Semiconductor ETF</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SOXX</v>
+      </c>
+      <c r="C18">
+        <v>2.8</v>
+      </c>
+      <c r="D18">
+        <v>528.29</v>
+      </c>
+      <c r="E18">
+        <v>1479.21</v>
+      </c>
+      <c r="F18">
+        <v>198.74</v>
+      </c>
+      <c r="G18">
+        <v>556.47</v>
+      </c>
+      <c r="H18">
+        <v>922.74</v>
+      </c>
+      <c r="I18">
+        <v>165.82</v>
+      </c>
+      <c r="J18">
+        <v>34.44</v>
+      </c>
+      <c r="K18">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ISHARES MSCI UAE ETF</v>
+      </c>
+      <c r="B19" t="str">
+        <v>UAE</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>18.97</v>
+      </c>
+      <c r="E19">
+        <v>284.55</v>
+      </c>
+      <c r="F19">
+        <v>18.25</v>
+      </c>
+      <c r="G19">
+        <v>273.81</v>
+      </c>
+      <c r="H19">
+        <v>10.74</v>
+      </c>
+      <c r="I19">
+        <v>3.92</v>
+      </c>
+      <c r="J19">
+        <v>-0.45</v>
+      </c>
+      <c r="K19">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>S&amp;P 500 Vanguard ETF</v>
+      </c>
+      <c r="B20" t="str">
         <v>VOO</v>
       </c>
-      <c r="C16">
-        <v>1.925</v>
-      </c>
-      <c r="D16">
-        <v>532.4</v>
-      </c>
-      <c r="E16">
-        <v>1024.87</v>
-      </c>
-      <c r="F16">
-        <v>503.37</v>
-      </c>
-      <c r="G16">
-        <v>969</v>
-      </c>
-      <c r="H16">
-        <v>55.87</v>
-      </c>
-      <c r="I16">
-        <v>5.77</v>
-      </c>
-      <c r="J16">
-        <v>-6.97</v>
-      </c>
-      <c r="K16">
-        <v>-0.68</v>
+      <c r="C20">
+        <v>0.925</v>
+      </c>
+      <c r="D20">
+        <v>682.41</v>
+      </c>
+      <c r="E20">
+        <v>631.23</v>
+      </c>
+      <c r="F20">
+        <v>483.66</v>
+      </c>
+      <c r="G20">
+        <v>447.39</v>
+      </c>
+      <c r="H20">
+        <v>183.84</v>
+      </c>
+      <c r="I20">
+        <v>41.09</v>
+      </c>
+      <c r="J20">
+        <v>3.46</v>
+      </c>
+      <c r="K20">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>State Street Health Care Select Sector SPDR ETF</v>
+      </c>
+      <c r="B21" t="str">
+        <v>XLV</v>
+      </c>
+      <c r="C21">
+        <v>7.25</v>
+      </c>
+      <c r="D21">
+        <v>146.71</v>
+      </c>
+      <c r="E21">
+        <v>1063.65</v>
+      </c>
+      <c r="F21">
+        <v>137.73</v>
+      </c>
+      <c r="G21">
+        <v>998.53</v>
+      </c>
+      <c r="H21">
+        <v>65.12</v>
+      </c>
+      <c r="I21">
+        <v>6.52</v>
+      </c>
+      <c r="J21">
+        <v>6.24</v>
+      </c>
+      <c r="K21">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
   </ignoredErrors>
 </worksheet>
 </file>